--- a/cms/Directorio.xlsx
+++ b/cms/Directorio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ecesar\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE46A9A6-0DE2-4091-BFEE-708A63F1CF3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{142B5CB3-2C1D-404A-A08A-DCBB4E6EA20B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{0F1940CD-ED30-440E-B603-2BB4143331FF}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1119" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1492" uniqueCount="414">
   <si>
     <t>CC</t>
   </si>
@@ -1269,6 +1269,18 @@
   </si>
   <si>
     <t>Parque Jadin kiosko</t>
+  </si>
+  <si>
+    <t>Estatus</t>
+  </si>
+  <si>
+    <t>Abierta</t>
+  </si>
+  <si>
+    <t>Cierre Temporal</t>
+  </si>
+  <si>
+    <t>Cierre Definitivo</t>
   </si>
 </sst>
 </file>
@@ -1340,7 +1352,107 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="20">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1773,15 +1885,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C74F270B-DB38-4B3D-96E2-1FE948E11503}">
-  <dimension ref="A1:D373"/>
+  <dimension ref="A1:E373"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="19.26953125" customWidth="1"/>
     <col min="3" max="3" width="18.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="39.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="39.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="28">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1792,10 +1905,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:5">
       <c r="A2" s="2">
         <v>38101</v>
       </c>
@@ -1805,11 +1921,14 @@
       <c r="C2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:5">
       <c r="A3" s="2">
         <v>38103</v>
       </c>
@@ -1819,11 +1938,14 @@
       <c r="C3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:5">
       <c r="A4" s="2">
         <v>38104</v>
       </c>
@@ -1833,11 +1955,14 @@
       <c r="C4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:5">
       <c r="A5" s="2">
         <v>38106</v>
       </c>
@@ -1847,11 +1972,14 @@
       <c r="C5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:5">
       <c r="A6" s="2">
         <v>38107</v>
       </c>
@@ -1861,11 +1989,14 @@
       <c r="C6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:5">
       <c r="A7" s="2">
         <v>38108</v>
       </c>
@@ -1875,11 +2006,14 @@
       <c r="C7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:5">
       <c r="A8" s="2">
         <v>38109</v>
       </c>
@@ -1889,11 +2023,14 @@
       <c r="C8" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:5">
       <c r="A9" s="2">
         <v>38110</v>
       </c>
@@ -1903,11 +2040,14 @@
       <c r="C9" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:5">
       <c r="A10" s="2">
         <v>38111</v>
       </c>
@@ -1917,11 +2057,14 @@
       <c r="C10" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:5">
       <c r="A11" s="2">
         <v>38112</v>
       </c>
@@ -1931,11 +2074,14 @@
       <c r="C11" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:5">
       <c r="A12" s="2">
         <v>38113</v>
       </c>
@@ -1945,11 +2091,14 @@
       <c r="C12" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E12" s="4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:5">
       <c r="A13" s="2">
         <v>38114</v>
       </c>
@@ -1959,11 +2108,14 @@
       <c r="C13" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E13" s="4" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:5">
       <c r="A14" s="2">
         <v>38115</v>
       </c>
@@ -1973,11 +2125,14 @@
       <c r="C14" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E14" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:5">
       <c r="A15" s="2">
         <v>38116</v>
       </c>
@@ -1987,11 +2142,14 @@
       <c r="C15" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E15" s="4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:5">
       <c r="A16" s="2">
         <v>38117</v>
       </c>
@@ -2001,11 +2159,14 @@
       <c r="C16" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E16" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:5">
       <c r="A17" s="2">
         <v>38118</v>
       </c>
@@ -2015,11 +2176,14 @@
       <c r="C17" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E17" s="4" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:5">
       <c r="A18" s="2">
         <v>38119</v>
       </c>
@@ -2029,11 +2193,14 @@
       <c r="C18" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E18" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:5">
       <c r="A19" s="2">
         <v>38121</v>
       </c>
@@ -2043,11 +2210,14 @@
       <c r="C19" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E19" s="4" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:5">
       <c r="A20" s="2">
         <v>38122</v>
       </c>
@@ -2057,11 +2227,14 @@
       <c r="C20" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E20" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:5">
       <c r="A21" s="2">
         <v>38123</v>
       </c>
@@ -2071,11 +2244,14 @@
       <c r="C21" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E21" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:5">
       <c r="A22" s="2">
         <v>38124</v>
       </c>
@@ -2085,11 +2261,14 @@
       <c r="C22" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E22" s="4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:5">
       <c r="A23" s="2">
         <v>38126</v>
       </c>
@@ -2099,11 +2278,14 @@
       <c r="C23" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E23" s="4" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:5">
       <c r="A24" s="2">
         <v>38128</v>
       </c>
@@ -2113,11 +2295,14 @@
       <c r="C24" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E24" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:5">
       <c r="A25" s="2">
         <v>38129</v>
       </c>
@@ -2127,11 +2312,14 @@
       <c r="C25" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E25" s="4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:5">
       <c r="A26" s="2">
         <v>38131</v>
       </c>
@@ -2141,11 +2329,14 @@
       <c r="C26" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E26" s="4" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:5">
       <c r="A27" s="2">
         <v>38134</v>
       </c>
@@ -2155,11 +2346,14 @@
       <c r="C27" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E27" s="4" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:5">
       <c r="A28" s="2">
         <v>38135</v>
       </c>
@@ -2169,11 +2363,14 @@
       <c r="C28" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="E28" s="4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:5">
       <c r="A29" s="2">
         <v>38136</v>
       </c>
@@ -2183,11 +2380,14 @@
       <c r="C29" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E29" s="4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:5">
       <c r="A30" s="2">
         <v>38138</v>
       </c>
@@ -2197,11 +2397,14 @@
       <c r="C30" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E30" s="4" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:5">
       <c r="A31" s="2">
         <v>38139</v>
       </c>
@@ -2211,11 +2414,14 @@
       <c r="C31" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D31" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E31" s="4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:5">
       <c r="A32" s="2">
         <v>38141</v>
       </c>
@@ -2225,11 +2431,14 @@
       <c r="C32" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E32" s="4" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33" spans="1:5">
       <c r="A33" s="2">
         <v>38142</v>
       </c>
@@ -2239,11 +2448,14 @@
       <c r="C33" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="D33" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E33" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="34" spans="1:4">
+    <row r="34" spans="1:5">
       <c r="A34" s="2">
         <v>38148</v>
       </c>
@@ -2253,11 +2465,14 @@
       <c r="C34" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D34" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E34" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
+    <row r="35" spans="1:5">
       <c r="A35" s="2">
         <v>38149</v>
       </c>
@@ -2267,11 +2482,14 @@
       <c r="C35" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="D35" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E35" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
+    <row r="36" spans="1:5">
       <c r="A36" s="2">
         <v>38150</v>
       </c>
@@ -2281,11 +2499,14 @@
       <c r="C36" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D36" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E36" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37" spans="1:5">
       <c r="A37" s="2">
         <v>38151</v>
       </c>
@@ -2295,11 +2516,14 @@
       <c r="C37" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="D37" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E37" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" spans="1:5">
       <c r="A38" s="2">
         <v>38152</v>
       </c>
@@ -2309,11 +2533,14 @@
       <c r="C38" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="D38" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E38" s="4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:5">
       <c r="A39" s="2">
         <v>38155</v>
       </c>
@@ -2323,11 +2550,14 @@
       <c r="C39" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D39" s="4" t="s">
+      <c r="D39" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E39" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40" spans="1:5">
       <c r="A40" s="2">
         <v>38156</v>
       </c>
@@ -2337,11 +2567,14 @@
       <c r="C40" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="D40" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="E40" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:5">
       <c r="A41" s="2">
         <v>38158</v>
       </c>
@@ -2351,11 +2584,14 @@
       <c r="C41" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D41" s="4" t="s">
+      <c r="D41" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E41" s="4" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="42" spans="1:4">
+    <row r="42" spans="1:5">
       <c r="A42" s="2">
         <v>38166</v>
       </c>
@@ -2365,11 +2601,14 @@
       <c r="C42" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D42" s="4" t="s">
+      <c r="D42" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E42" s="4" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="43" spans="1:4">
+    <row r="43" spans="1:5">
       <c r="A43" s="2">
         <v>38167</v>
       </c>
@@ -2379,11 +2618,14 @@
       <c r="C43" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D43" s="4" t="s">
+      <c r="D43" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E43" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="44" spans="1:4">
+    <row r="44" spans="1:5">
       <c r="A44" s="2">
         <v>38168</v>
       </c>
@@ -2393,11 +2635,14 @@
       <c r="C44" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D44" s="4" t="s">
+      <c r="D44" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="E44" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="45" spans="1:4">
+    <row r="45" spans="1:5">
       <c r="A45" s="2">
         <v>38169</v>
       </c>
@@ -2407,11 +2652,14 @@
       <c r="C45" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D45" s="4" t="s">
+      <c r="D45" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E45" s="4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="46" spans="1:4">
+    <row r="46" spans="1:5">
       <c r="A46" s="2">
         <v>38171</v>
       </c>
@@ -2421,11 +2669,14 @@
       <c r="C46" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="D46" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E46" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="47" spans="1:4">
+    <row r="47" spans="1:5">
       <c r="A47" s="2">
         <v>38172</v>
       </c>
@@ -2435,11 +2686,14 @@
       <c r="C47" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D47" s="4" t="s">
+      <c r="D47" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E47" s="4" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="48" spans="1:4">
+    <row r="48" spans="1:5">
       <c r="A48" s="2">
         <v>38173</v>
       </c>
@@ -2449,11 +2703,14 @@
       <c r="C48" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D48" s="4" t="s">
+      <c r="D48" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E48" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="49" spans="1:4">
+    <row r="49" spans="1:5">
       <c r="A49" s="2">
         <v>38176</v>
       </c>
@@ -2463,11 +2720,14 @@
       <c r="C49" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D49" s="4" t="s">
+      <c r="D49" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E49" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="50" spans="1:4">
+    <row r="50" spans="1:5">
       <c r="A50" s="2">
         <v>38179</v>
       </c>
@@ -2477,11 +2737,14 @@
       <c r="C50" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D50" s="4" t="s">
+      <c r="D50" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E50" s="4" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="51" spans="1:4">
+    <row r="51" spans="1:5">
       <c r="A51" s="2">
         <v>38182</v>
       </c>
@@ -2491,11 +2754,14 @@
       <c r="C51" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D51" s="4" t="s">
+      <c r="D51" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E51" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="52" spans="1:4">
+    <row r="52" spans="1:5">
       <c r="A52" s="2">
         <v>38185</v>
       </c>
@@ -2505,11 +2771,14 @@
       <c r="C52" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D52" s="4" t="s">
+      <c r="D52" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E52" s="4" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="53" spans="1:4">
+    <row r="53" spans="1:5">
       <c r="A53" s="2">
         <v>38186</v>
       </c>
@@ -2519,11 +2788,14 @@
       <c r="C53" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D53" s="4" t="s">
+      <c r="D53" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E53" s="4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="54" spans="1:4">
+    <row r="54" spans="1:5">
       <c r="A54" s="2">
         <v>38187</v>
       </c>
@@ -2533,11 +2805,14 @@
       <c r="C54" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D54" s="4" t="s">
+      <c r="D54" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E54" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="55" spans="1:4">
+    <row r="55" spans="1:5">
       <c r="A55" s="2">
         <v>38188</v>
       </c>
@@ -2547,11 +2822,14 @@
       <c r="C55" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D55" s="4" t="s">
+      <c r="D55" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E55" s="4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="56" spans="1:4">
+    <row r="56" spans="1:5">
       <c r="A56" s="2">
         <v>38189</v>
       </c>
@@ -2561,11 +2839,14 @@
       <c r="C56" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D56" s="4" t="s">
+      <c r="D56" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E56" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="57" spans="1:4">
+    <row r="57" spans="1:5">
       <c r="A57" s="2">
         <v>38191</v>
       </c>
@@ -2575,11 +2856,14 @@
       <c r="C57" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D57" s="4" t="s">
+      <c r="D57" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E57" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="58" spans="1:4">
+    <row r="58" spans="1:5">
       <c r="A58" s="2">
         <v>38193</v>
       </c>
@@ -2589,11 +2873,14 @@
       <c r="C58" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D58" s="4" t="s">
+      <c r="D58" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E58" s="4" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="59" spans="1:4">
+    <row r="59" spans="1:5">
       <c r="A59" s="2">
         <v>38194</v>
       </c>
@@ -2603,11 +2890,14 @@
       <c r="C59" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D59" s="4" t="s">
+      <c r="D59" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E59" s="4" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="60" spans="1:4">
+    <row r="60" spans="1:5">
       <c r="A60" s="2">
         <v>38197</v>
       </c>
@@ -2617,11 +2907,14 @@
       <c r="C60" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D60" s="4" t="s">
+      <c r="D60" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E60" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="61" spans="1:4">
+    <row r="61" spans="1:5">
       <c r="A61" s="2">
         <v>38202</v>
       </c>
@@ -2631,11 +2924,14 @@
       <c r="C61" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D61" s="4" t="s">
+      <c r="D61" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="E61" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="62" spans="1:4">
+    <row r="62" spans="1:5">
       <c r="A62" s="2">
         <v>38203</v>
       </c>
@@ -2645,11 +2941,14 @@
       <c r="C62" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D62" s="4" t="s">
+      <c r="D62" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E62" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="63" spans="1:4">
+    <row r="63" spans="1:5">
       <c r="A63" s="2">
         <v>38205</v>
       </c>
@@ -2659,11 +2958,14 @@
       <c r="C63" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D63" s="4" t="s">
+      <c r="D63" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E63" s="4" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="64" spans="1:4">
+    <row r="64" spans="1:5">
       <c r="A64" s="2">
         <v>38207</v>
       </c>
@@ -2673,11 +2975,14 @@
       <c r="C64" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D64" s="4" t="s">
+      <c r="D64" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E64" s="4" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="65" spans="1:4">
+    <row r="65" spans="1:5">
       <c r="A65" s="2">
         <v>38208</v>
       </c>
@@ -2687,11 +2992,14 @@
       <c r="C65" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D65" s="4" t="s">
+      <c r="D65" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E65" s="4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="66" spans="1:4">
+    <row r="66" spans="1:5">
       <c r="A66" s="2">
         <v>38219</v>
       </c>
@@ -2701,11 +3009,14 @@
       <c r="C66" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D66" s="4" t="s">
+      <c r="D66" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E66" s="4" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="67" spans="1:4">
+    <row r="67" spans="1:5">
       <c r="A67" s="2">
         <v>38220</v>
       </c>
@@ -2715,11 +3026,14 @@
       <c r="C67" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D67" s="4" t="s">
+      <c r="D67" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E67" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="68" spans="1:4">
+    <row r="68" spans="1:5">
       <c r="A68" s="2">
         <v>38225</v>
       </c>
@@ -2729,11 +3043,14 @@
       <c r="C68" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D68" s="4" t="s">
+      <c r="D68" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E68" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="69" spans="1:4">
+    <row r="69" spans="1:5">
       <c r="A69" s="2">
         <v>38226</v>
       </c>
@@ -2743,11 +3060,14 @@
       <c r="C69" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D69" s="4" t="s">
+      <c r="D69" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E69" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="70" spans="1:4">
+    <row r="70" spans="1:5">
       <c r="A70" s="2">
         <v>38227</v>
       </c>
@@ -2757,11 +3077,14 @@
       <c r="C70" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D70" s="4" t="s">
+      <c r="D70" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E70" s="4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="71" spans="1:4">
+    <row r="71" spans="1:5">
       <c r="A71" s="2">
         <v>38230</v>
       </c>
@@ -2771,11 +3094,14 @@
       <c r="C71" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D71" s="4" t="s">
+      <c r="D71" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E71" s="4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="72" spans="1:4">
+    <row r="72" spans="1:5">
       <c r="A72" s="2">
         <v>38233</v>
       </c>
@@ -2785,11 +3111,14 @@
       <c r="C72" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D72" s="4" t="s">
+      <c r="D72" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E72" s="4" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="73" spans="1:4">
+    <row r="73" spans="1:5">
       <c r="A73" s="2">
         <v>38234</v>
       </c>
@@ -2799,11 +3128,14 @@
       <c r="C73" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D73" s="4" t="s">
+      <c r="D73" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E73" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="74" spans="1:4">
+    <row r="74" spans="1:5">
       <c r="A74" s="2">
         <v>38239</v>
       </c>
@@ -2813,11 +3145,14 @@
       <c r="C74" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D74" s="4" t="s">
+      <c r="D74" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E74" s="4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="75" spans="1:4">
+    <row r="75" spans="1:5">
       <c r="A75" s="2">
         <v>38240</v>
       </c>
@@ -2827,11 +3162,14 @@
       <c r="C75" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D75" s="4" t="s">
+      <c r="D75" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="E75" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="76" spans="1:4">
+    <row r="76" spans="1:5">
       <c r="A76" s="2">
         <v>38260</v>
       </c>
@@ -2841,11 +3179,14 @@
       <c r="C76" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D76" s="4" t="s">
+      <c r="D76" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E76" s="4" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="77" spans="1:4">
+    <row r="77" spans="1:5">
       <c r="A77" s="2">
         <v>38266</v>
       </c>
@@ -2855,11 +3196,14 @@
       <c r="C77" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D77" s="4" t="s">
+      <c r="D77" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E77" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="78" spans="1:4">
+    <row r="78" spans="1:5">
       <c r="A78" s="2">
         <v>38270</v>
       </c>
@@ -2869,11 +3213,14 @@
       <c r="C78" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D78" s="4" t="s">
+      <c r="D78" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E78" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="79" spans="1:4">
+    <row r="79" spans="1:5">
       <c r="A79" s="2">
         <v>38272</v>
       </c>
@@ -2883,11 +3230,14 @@
       <c r="C79" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D79" s="4" t="s">
+      <c r="D79" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E79" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="80" spans="1:4">
+    <row r="80" spans="1:5">
       <c r="A80" s="2">
         <v>38279</v>
       </c>
@@ -2897,11 +3247,14 @@
       <c r="C80" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D80" s="4" t="s">
+      <c r="D80" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E80" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="81" spans="1:4">
+    <row r="81" spans="1:5">
       <c r="A81" s="2">
         <v>38285</v>
       </c>
@@ -2911,11 +3264,14 @@
       <c r="C81" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D81" s="4" t="s">
+      <c r="D81" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E81" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="82" spans="1:4">
+    <row r="82" spans="1:5">
       <c r="A82" s="2">
         <v>38289</v>
       </c>
@@ -2925,11 +3281,14 @@
       <c r="C82" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D82" s="4" t="s">
+      <c r="D82" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E82" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="83" spans="1:4">
+    <row r="83" spans="1:5">
       <c r="A83" s="2">
         <v>38291</v>
       </c>
@@ -2939,11 +3298,14 @@
       <c r="C83" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D83" s="4" t="s">
+      <c r="D83" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E83" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="84" spans="1:4">
+    <row r="84" spans="1:5">
       <c r="A84" s="2">
         <v>38292</v>
       </c>
@@ -2953,11 +3315,14 @@
       <c r="C84" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D84" s="4" t="s">
+      <c r="D84" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E84" s="4" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="85" spans="1:4">
+    <row r="85" spans="1:5">
       <c r="A85" s="2">
         <v>38297</v>
       </c>
@@ -2967,11 +3332,14 @@
       <c r="C85" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D85" s="4" t="s">
+      <c r="D85" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E85" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="86" spans="1:4">
+    <row r="86" spans="1:5">
       <c r="A86" s="2">
         <v>38298</v>
       </c>
@@ -2981,11 +3349,14 @@
       <c r="C86" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D86" s="4" t="s">
+      <c r="D86" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E86" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="87" spans="1:4">
+    <row r="87" spans="1:5">
       <c r="A87" s="2">
         <v>38299</v>
       </c>
@@ -2995,11 +3366,14 @@
       <c r="C87" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D87" s="4" t="s">
+      <c r="D87" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E87" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="88" spans="1:4">
+    <row r="88" spans="1:5">
       <c r="A88" s="2">
         <v>38312</v>
       </c>
@@ -3009,11 +3383,14 @@
       <c r="C88" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D88" s="4" t="s">
+      <c r="D88" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E88" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="89" spans="1:4">
+    <row r="89" spans="1:5">
       <c r="A89" s="2">
         <v>38319</v>
       </c>
@@ -3023,11 +3400,14 @@
       <c r="C89" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D89" s="4" t="s">
+      <c r="D89" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E89" s="4" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="90" spans="1:4">
+    <row r="90" spans="1:5">
       <c r="A90" s="2">
         <v>38333</v>
       </c>
@@ -3037,11 +3417,14 @@
       <c r="C90" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D90" s="4" t="s">
+      <c r="D90" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E90" s="4" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="91" spans="1:4">
+    <row r="91" spans="1:5">
       <c r="A91" s="2">
         <v>38339</v>
       </c>
@@ -3051,11 +3434,14 @@
       <c r="C91" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D91" s="4" t="s">
+      <c r="D91" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E91" s="4" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="92" spans="1:4">
+    <row r="92" spans="1:5">
       <c r="A92" s="2">
         <v>38340</v>
       </c>
@@ -3065,11 +3451,14 @@
       <c r="C92" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D92" s="4" t="s">
+      <c r="D92" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E92" s="4" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="93" spans="1:4">
+    <row r="93" spans="1:5">
       <c r="A93" s="2">
         <v>38344</v>
       </c>
@@ -3079,11 +3468,14 @@
       <c r="C93" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D93" s="4" t="s">
+      <c r="D93" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E93" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="94" spans="1:4">
+    <row r="94" spans="1:5">
       <c r="A94" s="2">
         <v>38349</v>
       </c>
@@ -3093,11 +3485,14 @@
       <c r="C94" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D94" s="4" t="s">
+      <c r="D94" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E94" s="4" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="95" spans="1:4">
+    <row r="95" spans="1:5">
       <c r="A95" s="2">
         <v>38351</v>
       </c>
@@ -3107,11 +3502,14 @@
       <c r="C95" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D95" s="4" t="s">
+      <c r="D95" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E95" s="4" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="96" spans="1:4">
+    <row r="96" spans="1:5">
       <c r="A96" s="2">
         <v>38360</v>
       </c>
@@ -3121,11 +3519,14 @@
       <c r="C96" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D96" s="4" t="s">
+      <c r="D96" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E96" s="4" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="97" spans="1:4">
+    <row r="97" spans="1:5">
       <c r="A97" s="2">
         <v>38361</v>
       </c>
@@ -3135,11 +3536,14 @@
       <c r="C97" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D97" s="4" t="s">
+      <c r="D97" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E97" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="98" spans="1:4">
+    <row r="98" spans="1:5">
       <c r="A98" s="2">
         <v>38363</v>
       </c>
@@ -3149,11 +3553,14 @@
       <c r="C98" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D98" s="4" t="s">
+      <c r="D98" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E98" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="99" spans="1:4">
+    <row r="99" spans="1:5">
       <c r="A99" s="2">
         <v>38365</v>
       </c>
@@ -3163,11 +3570,14 @@
       <c r="C99" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D99" s="4" t="s">
+      <c r="D99" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E99" s="4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="100" spans="1:4">
+    <row r="100" spans="1:5">
       <c r="A100" s="2">
         <v>38366</v>
       </c>
@@ -3177,11 +3587,14 @@
       <c r="C100" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D100" s="4" t="s">
+      <c r="D100" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E100" s="4" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="101" spans="1:4">
+    <row r="101" spans="1:5">
       <c r="A101" s="2">
         <v>38367</v>
       </c>
@@ -3191,11 +3604,14 @@
       <c r="C101" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D101" s="4" t="s">
+      <c r="D101" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E101" s="4" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="102" spans="1:4">
+    <row r="102" spans="1:5">
       <c r="A102" s="2">
         <v>38368</v>
       </c>
@@ -3205,11 +3621,14 @@
       <c r="C102" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D102" s="4" t="s">
+      <c r="D102" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E102" s="4" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="103" spans="1:4">
+    <row r="103" spans="1:5">
       <c r="A103" s="2">
         <v>38371</v>
       </c>
@@ -3219,11 +3638,14 @@
       <c r="C103" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D103" s="4" t="s">
+      <c r="D103" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E103" s="4" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="104" spans="1:4">
+    <row r="104" spans="1:5">
       <c r="A104" s="2">
         <v>38372</v>
       </c>
@@ -3233,11 +3655,14 @@
       <c r="C104" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D104" s="4" t="s">
+      <c r="D104" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E104" s="4" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="105" spans="1:4">
+    <row r="105" spans="1:5">
       <c r="A105" s="2">
         <v>38374</v>
       </c>
@@ -3247,11 +3672,14 @@
       <c r="C105" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D105" s="4" t="s">
+      <c r="D105" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E105" s="4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="106" spans="1:4">
+    <row r="106" spans="1:5">
       <c r="A106" s="2">
         <v>38375</v>
       </c>
@@ -3261,11 +3689,14 @@
       <c r="C106" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D106" s="4" t="s">
+      <c r="D106" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E106" s="4" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="107" spans="1:4">
+    <row r="107" spans="1:5">
       <c r="A107" s="2">
         <v>38376</v>
       </c>
@@ -3275,11 +3706,14 @@
       <c r="C107" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D107" s="4" t="s">
+      <c r="D107" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E107" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="108" spans="1:4">
+    <row r="108" spans="1:5">
       <c r="A108" s="2">
         <v>38378</v>
       </c>
@@ -3289,11 +3723,14 @@
       <c r="C108" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D108" s="4" t="s">
+      <c r="D108" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E108" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="109" spans="1:4">
+    <row r="109" spans="1:5">
       <c r="A109" s="2">
         <v>38379</v>
       </c>
@@ -3303,11 +3740,14 @@
       <c r="C109" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D109" s="4" t="s">
+      <c r="D109" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E109" s="4" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="110" spans="1:4">
+    <row r="110" spans="1:5">
       <c r="A110" s="2">
         <v>38382</v>
       </c>
@@ -3317,11 +3757,14 @@
       <c r="C110" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D110" s="4" t="s">
+      <c r="D110" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E110" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="111" spans="1:4">
+    <row r="111" spans="1:5">
       <c r="A111" s="2">
         <v>38386</v>
       </c>
@@ -3331,11 +3774,14 @@
       <c r="C111" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D111" s="4" t="s">
+      <c r="D111" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E111" s="4" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="112" spans="1:4">
+    <row r="112" spans="1:5">
       <c r="A112" s="2">
         <v>38389</v>
       </c>
@@ -3345,11 +3791,14 @@
       <c r="C112" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D112" s="4" t="s">
+      <c r="D112" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E112" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="113" spans="1:4">
+    <row r="113" spans="1:5">
       <c r="A113" s="2">
         <v>38390</v>
       </c>
@@ -3359,11 +3808,14 @@
       <c r="C113" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D113" s="4" t="s">
+      <c r="D113" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E113" s="4" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="114" spans="1:4">
+    <row r="114" spans="1:5">
       <c r="A114" s="2">
         <v>38393</v>
       </c>
@@ -3373,11 +3825,14 @@
       <c r="C114" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D114" s="4" t="s">
+      <c r="D114" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E114" s="4" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="115" spans="1:4">
+    <row r="115" spans="1:5">
       <c r="A115" s="2">
         <v>38394</v>
       </c>
@@ -3387,11 +3842,14 @@
       <c r="C115" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D115" s="4" t="s">
+      <c r="D115" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E115" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="116" spans="1:4">
+    <row r="116" spans="1:5">
       <c r="A116" s="2">
         <v>38398</v>
       </c>
@@ -3401,11 +3859,14 @@
       <c r="C116" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D116" s="4" t="s">
+      <c r="D116" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E116" s="4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="117" spans="1:4">
+    <row r="117" spans="1:5">
       <c r="A117" s="2">
         <v>38399</v>
       </c>
@@ -3415,11 +3876,14 @@
       <c r="C117" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D117" s="4" t="s">
+      <c r="D117" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E117" s="4" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="118" spans="1:4">
+    <row r="118" spans="1:5">
       <c r="A118" s="2">
         <v>38400</v>
       </c>
@@ -3429,11 +3893,14 @@
       <c r="C118" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D118" s="4" t="s">
+      <c r="D118" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E118" s="4" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="119" spans="1:4">
+    <row r="119" spans="1:5">
       <c r="A119" s="2">
         <v>38401</v>
       </c>
@@ -3443,11 +3910,14 @@
       <c r="C119" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D119" s="4" t="s">
+      <c r="D119" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E119" s="4" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="120" spans="1:4">
+    <row r="120" spans="1:5">
       <c r="A120" s="2">
         <v>38402</v>
       </c>
@@ -3457,11 +3927,14 @@
       <c r="C120" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D120" s="4" t="s">
+      <c r="D120" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E120" s="4" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="121" spans="1:4">
+    <row r="121" spans="1:5">
       <c r="A121" s="2">
         <v>38404</v>
       </c>
@@ -3471,11 +3944,14 @@
       <c r="C121" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D121" s="4" t="s">
+      <c r="D121" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E121" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="122" spans="1:4">
+    <row r="122" spans="1:5">
       <c r="A122" s="2">
         <v>38405</v>
       </c>
@@ -3485,11 +3961,14 @@
       <c r="C122" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D122" s="4" t="s">
+      <c r="D122" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E122" s="4" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="123" spans="1:4">
+    <row r="123" spans="1:5">
       <c r="A123" s="2">
         <v>38406</v>
       </c>
@@ -3499,11 +3978,14 @@
       <c r="C123" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D123" s="4" t="s">
+      <c r="D123" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E123" s="4" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="124" spans="1:4">
+    <row r="124" spans="1:5">
       <c r="A124" s="2">
         <v>38411</v>
       </c>
@@ -3513,11 +3995,14 @@
       <c r="C124" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D124" s="4" t="s">
+      <c r="D124" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E124" s="4" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="125" spans="1:4">
+    <row r="125" spans="1:5">
       <c r="A125" s="2">
         <v>38414</v>
       </c>
@@ -3527,11 +4012,14 @@
       <c r="C125" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D125" s="4" t="s">
+      <c r="D125" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E125" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="126" spans="1:4">
+    <row r="126" spans="1:5">
       <c r="A126" s="2">
         <v>38415</v>
       </c>
@@ -3541,11 +4029,14 @@
       <c r="C126" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D126" s="4" t="s">
+      <c r="D126" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E126" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="127" spans="1:4">
+    <row r="127" spans="1:5">
       <c r="A127" s="2">
         <v>38416</v>
       </c>
@@ -3555,11 +4046,14 @@
       <c r="C127" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D127" s="4" t="s">
+      <c r="D127" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E127" s="4" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="128" spans="1:4">
+    <row r="128" spans="1:5">
       <c r="A128" s="2">
         <v>38417</v>
       </c>
@@ -3569,11 +4063,14 @@
       <c r="C128" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D128" s="4" t="s">
+      <c r="D128" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E128" s="4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="129" spans="1:4">
+    <row r="129" spans="1:5">
       <c r="A129" s="2">
         <v>38418</v>
       </c>
@@ -3583,11 +4080,14 @@
       <c r="C129" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D129" s="4" t="s">
+      <c r="D129" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E129" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="130" spans="1:4">
+    <row r="130" spans="1:5">
       <c r="A130" s="2">
         <v>38419</v>
       </c>
@@ -3597,11 +4097,14 @@
       <c r="C130" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D130" s="4" t="s">
+      <c r="D130" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E130" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="131" spans="1:4">
+    <row r="131" spans="1:5">
       <c r="A131" s="2">
         <v>38422</v>
       </c>
@@ -3611,11 +4114,14 @@
       <c r="C131" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D131" s="4" t="s">
+      <c r="D131" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E131" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="132" spans="1:4">
+    <row r="132" spans="1:5">
       <c r="A132" s="2">
         <v>38423</v>
       </c>
@@ -3625,11 +4131,14 @@
       <c r="C132" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D132" s="4" t="s">
+      <c r="D132" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E132" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="133" spans="1:4">
+    <row r="133" spans="1:5">
       <c r="A133" s="2">
         <v>38427</v>
       </c>
@@ -3639,11 +4148,14 @@
       <c r="C133" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D133" s="4" t="s">
+      <c r="D133" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E133" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="134" spans="1:4">
+    <row r="134" spans="1:5">
       <c r="A134" s="2">
         <v>38428</v>
       </c>
@@ -3653,11 +4165,14 @@
       <c r="C134" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D134" s="4" t="s">
+      <c r="D134" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E134" s="4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="135" spans="1:4">
+    <row r="135" spans="1:5">
       <c r="A135" s="2">
         <v>38429</v>
       </c>
@@ -3667,11 +4182,14 @@
       <c r="C135" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D135" s="4" t="s">
+      <c r="D135" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E135" s="4" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="136" spans="1:4">
+    <row r="136" spans="1:5">
       <c r="A136" s="2">
         <v>38430</v>
       </c>
@@ -3681,11 +4199,14 @@
       <c r="C136" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D136" s="4" t="s">
+      <c r="D136" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E136" s="4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="137" spans="1:4">
+    <row r="137" spans="1:5">
       <c r="A137" s="2">
         <v>38431</v>
       </c>
@@ -3695,11 +4216,14 @@
       <c r="C137" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D137" s="4" t="s">
+      <c r="D137" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E137" s="4" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="138" spans="1:4">
+    <row r="138" spans="1:5">
       <c r="A138" s="2">
         <v>38432</v>
       </c>
@@ -3709,11 +4233,14 @@
       <c r="C138" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D138" s="4" t="s">
+      <c r="D138" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E138" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="139" spans="1:4">
+    <row r="139" spans="1:5">
       <c r="A139" s="2">
         <v>38433</v>
       </c>
@@ -3723,11 +4250,14 @@
       <c r="C139" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D139" s="4" t="s">
+      <c r="D139" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E139" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="140" spans="1:4">
+    <row r="140" spans="1:5">
       <c r="A140" s="2">
         <v>38438</v>
       </c>
@@ -3737,11 +4267,14 @@
       <c r="C140" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D140" s="4" t="s">
+      <c r="D140" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E140" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="141" spans="1:4">
+    <row r="141" spans="1:5">
       <c r="A141" s="2">
         <v>38439</v>
       </c>
@@ -3751,11 +4284,14 @@
       <c r="C141" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D141" s="4" t="s">
+      <c r="D141" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E141" s="4" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="142" spans="1:4">
+    <row r="142" spans="1:5">
       <c r="A142" s="2">
         <v>38440</v>
       </c>
@@ -3765,11 +4301,14 @@
       <c r="C142" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D142" s="4" t="s">
+      <c r="D142" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E142" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="143" spans="1:4">
+    <row r="143" spans="1:5">
       <c r="A143" s="2">
         <v>38441</v>
       </c>
@@ -3779,11 +4318,14 @@
       <c r="C143" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D143" s="4" t="s">
+      <c r="D143" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E143" s="4" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="144" spans="1:4">
+    <row r="144" spans="1:5">
       <c r="A144" s="2">
         <v>38442</v>
       </c>
@@ -3793,11 +4335,14 @@
       <c r="C144" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D144" s="4" t="s">
+      <c r="D144" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E144" s="4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="145" spans="1:4">
+    <row r="145" spans="1:5">
       <c r="A145" s="2">
         <v>38445</v>
       </c>
@@ -3807,11 +4352,14 @@
       <c r="C145" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D145" s="4" t="s">
+      <c r="D145" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E145" s="4" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="146" spans="1:4">
+    <row r="146" spans="1:5">
       <c r="A146" s="2">
         <v>38447</v>
       </c>
@@ -3821,11 +4369,14 @@
       <c r="C146" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D146" s="4" t="s">
+      <c r="D146" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E146" s="4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="147" spans="1:4">
+    <row r="147" spans="1:5">
       <c r="A147" s="2">
         <v>38452</v>
       </c>
@@ -3835,11 +4386,14 @@
       <c r="C147" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D147" s="4" t="s">
+      <c r="D147" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E147" s="4" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="148" spans="1:4">
+    <row r="148" spans="1:5">
       <c r="A148" s="2">
         <v>38455</v>
       </c>
@@ -3849,9 +4403,12 @@
       <c r="C148" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D148" s="4"/>
-    </row>
-    <row r="149" spans="1:4">
+      <c r="D148" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="E148" s="4"/>
+    </row>
+    <row r="149" spans="1:5">
       <c r="A149" s="2">
         <v>38456</v>
       </c>
@@ -3861,11 +4418,14 @@
       <c r="C149" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D149" s="4" t="s">
+      <c r="D149" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E149" s="4" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="150" spans="1:4">
+    <row r="150" spans="1:5">
       <c r="A150" s="2">
         <v>38458</v>
       </c>
@@ -3875,11 +4435,14 @@
       <c r="C150" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D150" s="4" t="s">
+      <c r="D150" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E150" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="151" spans="1:4">
+    <row r="151" spans="1:5">
       <c r="A151" s="2">
         <v>38460</v>
       </c>
@@ -3889,11 +4452,14 @@
       <c r="C151" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D151" s="4" t="s">
+      <c r="D151" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E151" s="4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="152" spans="1:4">
+    <row r="152" spans="1:5">
       <c r="A152" s="2">
         <v>38461</v>
       </c>
@@ -3903,11 +4469,14 @@
       <c r="C152" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D152" s="4" t="s">
+      <c r="D152" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E152" s="4" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="153" spans="1:4">
+    <row r="153" spans="1:5">
       <c r="A153" s="2">
         <v>38463</v>
       </c>
@@ -3917,11 +4486,14 @@
       <c r="C153" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D153" s="4" t="s">
+      <c r="D153" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E153" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="154" spans="1:4">
+    <row r="154" spans="1:5">
       <c r="A154" s="2">
         <v>38464</v>
       </c>
@@ -3931,11 +4503,14 @@
       <c r="C154" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D154" s="4" t="s">
+      <c r="D154" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E154" s="4" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="155" spans="1:4">
+    <row r="155" spans="1:5">
       <c r="A155" s="2">
         <v>38465</v>
       </c>
@@ -3945,11 +4520,14 @@
       <c r="C155" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D155" s="4" t="s">
+      <c r="D155" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E155" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="156" spans="1:4">
+    <row r="156" spans="1:5">
       <c r="A156" s="2">
         <v>38466</v>
       </c>
@@ -3959,11 +4537,14 @@
       <c r="C156" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D156" s="4" t="s">
+      <c r="D156" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E156" s="4" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="157" spans="1:4">
+    <row r="157" spans="1:5">
       <c r="A157" s="2">
         <v>38468</v>
       </c>
@@ -3973,11 +4554,14 @@
       <c r="C157" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D157" s="4" t="s">
+      <c r="D157" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E157" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="158" spans="1:4">
+    <row r="158" spans="1:5">
       <c r="A158" s="2">
         <v>38469</v>
       </c>
@@ -3987,11 +4571,14 @@
       <c r="C158" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D158" s="4" t="s">
+      <c r="D158" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E158" s="4" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="159" spans="1:4">
+    <row r="159" spans="1:5">
       <c r="A159" s="2">
         <v>38470</v>
       </c>
@@ -4001,11 +4588,14 @@
       <c r="C159" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D159" s="4" t="s">
+      <c r="D159" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E159" s="4" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="160" spans="1:4">
+    <row r="160" spans="1:5">
       <c r="A160" s="2">
         <v>38471</v>
       </c>
@@ -4015,11 +4605,14 @@
       <c r="C160" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D160" s="4" t="s">
+      <c r="D160" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E160" s="4" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="161" spans="1:4">
+    <row r="161" spans="1:5">
       <c r="A161" s="2">
         <v>38472</v>
       </c>
@@ -4029,11 +4622,14 @@
       <c r="C161" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D161" s="4" t="s">
+      <c r="D161" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E161" s="4" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="162" spans="1:4">
+    <row r="162" spans="1:5">
       <c r="A162" s="2">
         <v>38475</v>
       </c>
@@ -4043,11 +4639,14 @@
       <c r="C162" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D162" s="4" t="s">
+      <c r="D162" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E162" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="163" spans="1:4">
+    <row r="163" spans="1:5">
       <c r="A163" s="2">
         <v>38477</v>
       </c>
@@ -4057,11 +4656,14 @@
       <c r="C163" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D163" s="4" t="s">
+      <c r="D163" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E163" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="164" spans="1:4">
+    <row r="164" spans="1:5">
       <c r="A164" s="2">
         <v>38481</v>
       </c>
@@ -4071,11 +4673,14 @@
       <c r="C164" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D164" s="4" t="s">
+      <c r="D164" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E164" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="165" spans="1:4">
+    <row r="165" spans="1:5">
       <c r="A165" s="2">
         <v>38482</v>
       </c>
@@ -4085,11 +4690,14 @@
       <c r="C165" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D165" s="4" t="s">
+      <c r="D165" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E165" s="4" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="166" spans="1:4">
+    <row r="166" spans="1:5">
       <c r="A166" s="2">
         <v>38483</v>
       </c>
@@ -4099,11 +4707,14 @@
       <c r="C166" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D166" s="4" t="s">
+      <c r="D166" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E166" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="167" spans="1:4">
+    <row r="167" spans="1:5">
       <c r="A167" s="2">
         <v>38484</v>
       </c>
@@ -4113,11 +4724,14 @@
       <c r="C167" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D167" s="4" t="s">
+      <c r="D167" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E167" s="4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="168" spans="1:4">
+    <row r="168" spans="1:5">
       <c r="A168" s="2">
         <v>38485</v>
       </c>
@@ -4127,11 +4741,14 @@
       <c r="C168" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D168" s="4" t="s">
+      <c r="D168" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E168" s="4" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="169" spans="1:4">
+    <row r="169" spans="1:5">
       <c r="A169" s="2">
         <v>38487</v>
       </c>
@@ -4141,11 +4758,14 @@
       <c r="C169" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D169" s="4" t="s">
+      <c r="D169" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E169" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="170" spans="1:4">
+    <row r="170" spans="1:5">
       <c r="A170" s="2">
         <v>38494</v>
       </c>
@@ -4155,11 +4775,14 @@
       <c r="C170" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D170" s="4" t="s">
+      <c r="D170" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E170" s="4" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="171" spans="1:4">
+    <row r="171" spans="1:5">
       <c r="A171" s="2">
         <v>38496</v>
       </c>
@@ -4169,11 +4792,14 @@
       <c r="C171" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D171" s="4" t="s">
+      <c r="D171" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E171" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="172" spans="1:4">
+    <row r="172" spans="1:5">
       <c r="A172" s="2">
         <v>38497</v>
       </c>
@@ -4183,11 +4809,14 @@
       <c r="C172" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D172" s="4" t="s">
+      <c r="D172" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E172" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="173" spans="1:4">
+    <row r="173" spans="1:5">
       <c r="A173" s="2">
         <v>38498</v>
       </c>
@@ -4197,11 +4826,14 @@
       <c r="C173" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D173" s="4" t="s">
+      <c r="D173" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E173" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="174" spans="1:4">
+    <row r="174" spans="1:5">
       <c r="A174" s="2">
         <v>38499</v>
       </c>
@@ -4211,11 +4843,14 @@
       <c r="C174" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D174" s="4" t="s">
+      <c r="D174" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E174" s="4" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="175" spans="1:4">
+    <row r="175" spans="1:5">
       <c r="A175" s="2">
         <v>38501</v>
       </c>
@@ -4225,11 +4860,14 @@
       <c r="C175" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D175" s="4" t="s">
+      <c r="D175" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E175" s="4" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="176" spans="1:4">
+    <row r="176" spans="1:5">
       <c r="A176" s="2">
         <v>38502</v>
       </c>
@@ -4239,11 +4877,14 @@
       <c r="C176" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D176" s="4" t="s">
+      <c r="D176" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E176" s="4" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="177" spans="1:4">
+    <row r="177" spans="1:5">
       <c r="A177" s="2">
         <v>38504</v>
       </c>
@@ -4253,11 +4894,14 @@
       <c r="C177" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D177" s="4" t="s">
+      <c r="D177" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E177" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="178" spans="1:4">
+    <row r="178" spans="1:5">
       <c r="A178" s="2">
         <v>38507</v>
       </c>
@@ -4267,11 +4911,14 @@
       <c r="C178" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D178" s="4" t="s">
+      <c r="D178" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E178" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="179" spans="1:4">
+    <row r="179" spans="1:5">
       <c r="A179" s="2">
         <v>38508</v>
       </c>
@@ -4281,11 +4928,14 @@
       <c r="C179" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D179" s="4" t="s">
+      <c r="D179" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E179" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="180" spans="1:4">
+    <row r="180" spans="1:5">
       <c r="A180" s="2">
         <v>38511</v>
       </c>
@@ -4295,11 +4945,14 @@
       <c r="C180" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D180" s="4" t="s">
+      <c r="D180" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E180" s="4" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="181" spans="1:4">
+    <row r="181" spans="1:5">
       <c r="A181" s="2">
         <v>38512</v>
       </c>
@@ -4309,11 +4962,14 @@
       <c r="C181" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D181" s="4" t="s">
+      <c r="D181" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E181" s="4" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="182" spans="1:4">
+    <row r="182" spans="1:5">
       <c r="A182" s="2">
         <v>38513</v>
       </c>
@@ -4323,11 +4979,14 @@
       <c r="C182" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D182" s="4" t="s">
+      <c r="D182" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E182" s="4" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="183" spans="1:4">
+    <row r="183" spans="1:5">
       <c r="A183" s="2">
         <v>38515</v>
       </c>
@@ -4337,11 +4996,14 @@
       <c r="C183" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D183" s="4" t="s">
+      <c r="D183" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E183" s="4" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="184" spans="1:4">
+    <row r="184" spans="1:5">
       <c r="A184" s="2">
         <v>38522</v>
       </c>
@@ -4351,11 +5013,14 @@
       <c r="C184" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D184" s="4" t="s">
+      <c r="D184" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E184" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="185" spans="1:4">
+    <row r="185" spans="1:5">
       <c r="A185" s="2">
         <v>38526</v>
       </c>
@@ -4365,11 +5030,14 @@
       <c r="C185" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D185" s="4" t="s">
+      <c r="D185" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E185" s="4" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="186" spans="1:4">
+    <row r="186" spans="1:5">
       <c r="A186" s="2">
         <v>38527</v>
       </c>
@@ -4379,11 +5047,14 @@
       <c r="C186" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D186" s="4" t="s">
+      <c r="D186" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E186" s="4" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="187" spans="1:4">
+    <row r="187" spans="1:5">
       <c r="A187" s="2">
         <v>38529</v>
       </c>
@@ -4393,11 +5064,14 @@
       <c r="C187" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D187" s="4" t="s">
+      <c r="D187" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E187" s="4" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="188" spans="1:4">
+    <row r="188" spans="1:5">
       <c r="A188" s="2">
         <v>38530</v>
       </c>
@@ -4407,11 +5081,14 @@
       <c r="C188" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D188" s="4" t="s">
+      <c r="D188" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E188" s="4" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="189" spans="1:4">
+    <row r="189" spans="1:5">
       <c r="A189" s="2">
         <v>38532</v>
       </c>
@@ -4421,11 +5098,14 @@
       <c r="C189" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D189" s="4" t="s">
+      <c r="D189" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E189" s="4" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="190" spans="1:4">
+    <row r="190" spans="1:5">
       <c r="A190" s="2">
         <v>38534</v>
       </c>
@@ -4435,11 +5115,14 @@
       <c r="C190" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D190" s="4" t="s">
+      <c r="D190" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E190" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="191" spans="1:4">
+    <row r="191" spans="1:5">
       <c r="A191" s="2">
         <v>38535</v>
       </c>
@@ -4449,11 +5132,14 @@
       <c r="C191" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D191" s="4" t="s">
+      <c r="D191" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E191" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="192" spans="1:4">
+    <row r="192" spans="1:5">
       <c r="A192" s="2">
         <v>38538</v>
       </c>
@@ -4463,11 +5149,14 @@
       <c r="C192" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D192" s="4" t="s">
+      <c r="D192" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E192" s="4" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="193" spans="1:4">
+    <row r="193" spans="1:5">
       <c r="A193" s="2">
         <v>38541</v>
       </c>
@@ -4477,11 +5166,14 @@
       <c r="C193" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D193" s="4" t="s">
+      <c r="D193" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E193" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="194" spans="1:4">
+    <row r="194" spans="1:5">
       <c r="A194" s="2">
         <v>38543</v>
       </c>
@@ -4491,11 +5183,14 @@
       <c r="C194" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D194" s="4" t="s">
+      <c r="D194" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E194" s="4" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="195" spans="1:4">
+    <row r="195" spans="1:5">
       <c r="A195" s="2">
         <v>38544</v>
       </c>
@@ -4505,11 +5200,14 @@
       <c r="C195" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D195" s="4" t="s">
+      <c r="D195" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E195" s="4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="196" spans="1:4">
+    <row r="196" spans="1:5">
       <c r="A196" s="2">
         <v>38546</v>
       </c>
@@ -4519,11 +5217,14 @@
       <c r="C196" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D196" s="4" t="s">
+      <c r="D196" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E196" s="4" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="197" spans="1:4">
+    <row r="197" spans="1:5">
       <c r="A197" s="2">
         <v>38547</v>
       </c>
@@ -4533,11 +5234,14 @@
       <c r="C197" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D197" s="4" t="s">
+      <c r="D197" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E197" s="4" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="198" spans="1:4">
+    <row r="198" spans="1:5">
       <c r="A198" s="2">
         <v>38549</v>
       </c>
@@ -4547,11 +5251,14 @@
       <c r="C198" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D198" s="4" t="s">
+      <c r="D198" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E198" s="4" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="199" spans="1:4">
+    <row r="199" spans="1:5">
       <c r="A199" s="2">
         <v>38553</v>
       </c>
@@ -4561,11 +5268,14 @@
       <c r="C199" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D199" s="4" t="s">
+      <c r="D199" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E199" s="4" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="200" spans="1:4">
+    <row r="200" spans="1:5">
       <c r="A200" s="2">
         <v>38554</v>
       </c>
@@ -4575,11 +5285,14 @@
       <c r="C200" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D200" s="4" t="s">
+      <c r="D200" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E200" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="201" spans="1:4">
+    <row r="201" spans="1:5">
       <c r="A201" s="2">
         <v>38555</v>
       </c>
@@ -4589,11 +5302,14 @@
       <c r="C201" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D201" s="4" t="s">
+      <c r="D201" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E201" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="202" spans="1:4">
+    <row r="202" spans="1:5">
       <c r="A202" s="2">
         <v>38556</v>
       </c>
@@ -4603,11 +5319,14 @@
       <c r="C202" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D202" s="4" t="s">
+      <c r="D202" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E202" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="203" spans="1:4">
+    <row r="203" spans="1:5">
       <c r="A203" s="2">
         <v>38557</v>
       </c>
@@ -4617,11 +5336,14 @@
       <c r="C203" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D203" s="4" t="s">
+      <c r="D203" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E203" s="4" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="204" spans="1:4">
+    <row r="204" spans="1:5">
       <c r="A204" s="2">
         <v>38558</v>
       </c>
@@ -4631,11 +5353,14 @@
       <c r="C204" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D204" s="4" t="s">
+      <c r="D204" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E204" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="205" spans="1:4">
+    <row r="205" spans="1:5">
       <c r="A205" s="2">
         <v>38560</v>
       </c>
@@ -4645,11 +5370,14 @@
       <c r="C205" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D205" s="4" t="s">
+      <c r="D205" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E205" s="4" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="206" spans="1:4">
+    <row r="206" spans="1:5">
       <c r="A206" s="2">
         <v>38561</v>
       </c>
@@ -4659,11 +5387,14 @@
       <c r="C206" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D206" s="4" t="s">
+      <c r="D206" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E206" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="207" spans="1:4">
+    <row r="207" spans="1:5">
       <c r="A207" s="2">
         <v>38567</v>
       </c>
@@ -4673,11 +5404,14 @@
       <c r="C207" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D207" s="4" t="s">
+      <c r="D207" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E207" s="4" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="208" spans="1:4">
+    <row r="208" spans="1:5">
       <c r="A208" s="2">
         <v>38568</v>
       </c>
@@ -4687,11 +5421,14 @@
       <c r="C208" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D208" s="4" t="s">
+      <c r="D208" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E208" s="4" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="209" spans="1:4">
+    <row r="209" spans="1:5">
       <c r="A209" s="2">
         <v>38569</v>
       </c>
@@ -4701,11 +5438,14 @@
       <c r="C209" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D209" s="4" t="s">
+      <c r="D209" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E209" s="4" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="210" spans="1:4">
+    <row r="210" spans="1:5">
       <c r="A210" s="2">
         <v>38570</v>
       </c>
@@ -4715,11 +5455,14 @@
       <c r="C210" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D210" s="4" t="s">
+      <c r="D210" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E210" s="4" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="211" spans="1:4">
+    <row r="211" spans="1:5">
       <c r="A211" s="2">
         <v>38571</v>
       </c>
@@ -4729,11 +5472,14 @@
       <c r="C211" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D211" s="4" t="s">
+      <c r="D211" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E211" s="4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="212" spans="1:4">
+    <row r="212" spans="1:5">
       <c r="A212" s="2">
         <v>38578</v>
       </c>
@@ -4743,11 +5489,14 @@
       <c r="C212" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D212" s="4" t="s">
+      <c r="D212" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E212" s="4" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="213" spans="1:4">
+    <row r="213" spans="1:5">
       <c r="A213" s="2">
         <v>38579</v>
       </c>
@@ -4757,11 +5506,14 @@
       <c r="C213" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D213" s="4" t="s">
+      <c r="D213" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E213" s="4" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="214" spans="1:4">
+    <row r="214" spans="1:5">
       <c r="A214" s="2">
         <v>38580</v>
       </c>
@@ -4771,11 +5523,14 @@
       <c r="C214" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D214" s="4" t="s">
+      <c r="D214" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E214" s="4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="215" spans="1:4">
+    <row r="215" spans="1:5">
       <c r="A215" s="2">
         <v>38581</v>
       </c>
@@ -4785,11 +5540,14 @@
       <c r="C215" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D215" s="4" t="s">
+      <c r="D215" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E215" s="4" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="216" spans="1:4">
+    <row r="216" spans="1:5">
       <c r="A216" s="2">
         <v>38585</v>
       </c>
@@ -4799,11 +5557,14 @@
       <c r="C216" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D216" s="4" t="s">
+      <c r="D216" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E216" s="4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="217" spans="1:4">
+    <row r="217" spans="1:5">
       <c r="A217" s="2">
         <v>38587</v>
       </c>
@@ -4813,11 +5574,14 @@
       <c r="C217" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D217" s="4" t="s">
+      <c r="D217" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E217" s="4" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="218" spans="1:4">
+    <row r="218" spans="1:5">
       <c r="A218" s="2">
         <v>38590</v>
       </c>
@@ -4827,11 +5591,14 @@
       <c r="C218" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D218" s="4" t="s">
+      <c r="D218" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E218" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="219" spans="1:4">
+    <row r="219" spans="1:5">
       <c r="A219" s="2">
         <v>38594</v>
       </c>
@@ -4841,11 +5608,14 @@
       <c r="C219" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D219" s="4" t="s">
+      <c r="D219" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E219" s="4" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="220" spans="1:4">
+    <row r="220" spans="1:5">
       <c r="A220" s="2">
         <v>38597</v>
       </c>
@@ -4855,11 +5625,14 @@
       <c r="C220" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D220" s="4" t="s">
+      <c r="D220" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E220" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="221" spans="1:4">
+    <row r="221" spans="1:5">
       <c r="A221" s="2">
         <v>38600</v>
       </c>
@@ -4869,11 +5642,14 @@
       <c r="C221" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D221" s="4" t="s">
+      <c r="D221" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E221" s="4" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="222" spans="1:4">
+    <row r="222" spans="1:5">
       <c r="A222" s="2">
         <v>38602</v>
       </c>
@@ -4883,11 +5659,14 @@
       <c r="C222" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D222" s="4" t="s">
+      <c r="D222" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E222" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="223" spans="1:4">
+    <row r="223" spans="1:5">
       <c r="A223" s="2">
         <v>38604</v>
       </c>
@@ -4897,11 +5676,14 @@
       <c r="C223" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D223" s="4" t="s">
+      <c r="D223" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E223" s="4" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="224" spans="1:4">
+    <row r="224" spans="1:5">
       <c r="A224" s="2">
         <v>38605</v>
       </c>
@@ -4911,11 +5693,14 @@
       <c r="C224" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D224" s="4" t="s">
+      <c r="D224" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E224" s="4" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="225" spans="1:4">
+    <row r="225" spans="1:5">
       <c r="A225" s="2">
         <v>38606</v>
       </c>
@@ -4925,11 +5710,14 @@
       <c r="C225" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D225" s="4" t="s">
+      <c r="D225" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E225" s="4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="226" spans="1:4">
+    <row r="226" spans="1:5">
       <c r="A226" s="2">
         <v>38607</v>
       </c>
@@ -4939,11 +5727,14 @@
       <c r="C226" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D226" s="4" t="s">
+      <c r="D226" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E226" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="227" spans="1:4">
+    <row r="227" spans="1:5">
       <c r="A227" s="2">
         <v>38611</v>
       </c>
@@ -4953,11 +5744,14 @@
       <c r="C227" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D227" s="4" t="s">
+      <c r="D227" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E227" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="228" spans="1:4">
+    <row r="228" spans="1:5">
       <c r="A228" s="2">
         <v>38612</v>
       </c>
@@ -4967,11 +5761,14 @@
       <c r="C228" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D228" s="4" t="s">
+      <c r="D228" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E228" s="4" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="229" spans="1:4">
+    <row r="229" spans="1:5">
       <c r="A229" s="2">
         <v>38613</v>
       </c>
@@ -4981,11 +5778,14 @@
       <c r="C229" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D229" s="4" t="s">
+      <c r="D229" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="E229" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="230" spans="1:4">
+    <row r="230" spans="1:5">
       <c r="A230" s="2">
         <v>38615</v>
       </c>
@@ -4995,11 +5795,14 @@
       <c r="C230" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D230" s="4" t="s">
+      <c r="D230" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E230" s="4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="231" spans="1:4">
+    <row r="231" spans="1:5">
       <c r="A231" s="2">
         <v>38617</v>
       </c>
@@ -5009,11 +5812,14 @@
       <c r="C231" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D231" s="4" t="s">
+      <c r="D231" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E231" s="4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="232" spans="1:4">
+    <row r="232" spans="1:5">
       <c r="A232" s="2">
         <v>38619</v>
       </c>
@@ -5023,11 +5829,14 @@
       <c r="C232" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D232" s="4" t="s">
+      <c r="D232" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E232" s="4" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="233" spans="1:4">
+    <row r="233" spans="1:5">
       <c r="A233" s="2">
         <v>38620</v>
       </c>
@@ -5037,11 +5846,14 @@
       <c r="C233" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D233" s="4" t="s">
+      <c r="D233" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E233" s="4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="234" spans="1:4">
+    <row r="234" spans="1:5">
       <c r="A234" s="2">
         <v>38625</v>
       </c>
@@ -5051,11 +5863,14 @@
       <c r="C234" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D234" s="4" t="s">
+      <c r="D234" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E234" s="4" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="235" spans="1:4">
+    <row r="235" spans="1:5">
       <c r="A235" s="2">
         <v>38627</v>
       </c>
@@ -5065,11 +5880,14 @@
       <c r="C235" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D235" s="4" t="s">
+      <c r="D235" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E235" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="236" spans="1:4">
+    <row r="236" spans="1:5">
       <c r="A236" s="2">
         <v>38632</v>
       </c>
@@ -5079,11 +5897,14 @@
       <c r="C236" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D236" s="4" t="s">
+      <c r="D236" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="E236" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="237" spans="1:4">
+    <row r="237" spans="1:5">
       <c r="A237" s="2">
         <v>38633</v>
       </c>
@@ -5093,11 +5914,14 @@
       <c r="C237" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D237" s="4" t="s">
+      <c r="D237" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E237" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="238" spans="1:4">
+    <row r="238" spans="1:5">
       <c r="A238" s="2">
         <v>38635</v>
       </c>
@@ -5107,11 +5931,14 @@
       <c r="C238" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D238" s="4" t="s">
+      <c r="D238" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E238" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="239" spans="1:4">
+    <row r="239" spans="1:5">
       <c r="A239" s="2">
         <v>38637</v>
       </c>
@@ -5121,11 +5948,14 @@
       <c r="C239" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D239" s="4" t="s">
+      <c r="D239" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E239" s="4" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="240" spans="1:4">
+    <row r="240" spans="1:5">
       <c r="A240" s="2">
         <v>38644</v>
       </c>
@@ -5135,11 +5965,14 @@
       <c r="C240" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D240" s="4" t="s">
+      <c r="D240" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E240" s="4" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="241" spans="1:4">
+    <row r="241" spans="1:5">
       <c r="A241" s="2">
         <v>38645</v>
       </c>
@@ -5149,11 +5982,14 @@
       <c r="C241" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D241" s="4" t="s">
+      <c r="D241" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E241" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="242" spans="1:4">
+    <row r="242" spans="1:5">
       <c r="A242" s="2">
         <v>38646</v>
       </c>
@@ -5163,11 +5999,14 @@
       <c r="C242" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D242" s="4" t="s">
+      <c r="D242" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E242" s="4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="243" spans="1:4">
+    <row r="243" spans="1:5">
       <c r="A243" s="2">
         <v>38651</v>
       </c>
@@ -5177,11 +6016,14 @@
       <c r="C243" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D243" s="4" t="s">
+      <c r="D243" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E243" s="4" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="244" spans="1:4">
+    <row r="244" spans="1:5">
       <c r="A244" s="2">
         <v>38652</v>
       </c>
@@ -5191,11 +6033,14 @@
       <c r="C244" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D244" s="4" t="s">
+      <c r="D244" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="E244" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="245" spans="1:4">
+    <row r="245" spans="1:5">
       <c r="A245" s="2">
         <v>38653</v>
       </c>
@@ -5205,11 +6050,14 @@
       <c r="C245" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D245" s="4" t="s">
+      <c r="D245" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E245" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="246" spans="1:4">
+    <row r="246" spans="1:5">
       <c r="A246" s="2">
         <v>38654</v>
       </c>
@@ -5219,11 +6067,14 @@
       <c r="C246" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D246" s="4" t="s">
+      <c r="D246" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E246" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="247" spans="1:4">
+    <row r="247" spans="1:5">
       <c r="A247" s="2">
         <v>38656</v>
       </c>
@@ -5233,11 +6084,14 @@
       <c r="C247" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D247" s="4" t="s">
+      <c r="D247" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E247" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="248" spans="1:4">
+    <row r="248" spans="1:5">
       <c r="A248" s="2">
         <v>38657</v>
       </c>
@@ -5247,11 +6101,14 @@
       <c r="C248" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D248" s="4" t="s">
+      <c r="D248" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E248" s="4" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="249" spans="1:4">
+    <row r="249" spans="1:5">
       <c r="A249" s="2">
         <v>38658</v>
       </c>
@@ -5261,11 +6118,14 @@
       <c r="C249" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D249" s="4" t="s">
+      <c r="D249" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E249" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="250" spans="1:4">
+    <row r="250" spans="1:5">
       <c r="A250" s="2">
         <v>38659</v>
       </c>
@@ -5275,11 +6135,14 @@
       <c r="C250" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D250" s="4" t="s">
+      <c r="D250" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E250" s="4" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="251" spans="1:4">
+    <row r="251" spans="1:5">
       <c r="A251" s="2">
         <v>38661</v>
       </c>
@@ -5289,11 +6152,14 @@
       <c r="C251" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D251" s="4" t="s">
+      <c r="D251" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E251" s="4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="252" spans="1:4">
+    <row r="252" spans="1:5">
       <c r="A252" s="2">
         <v>38663</v>
       </c>
@@ -5303,11 +6169,14 @@
       <c r="C252" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D252" s="4" t="s">
+      <c r="D252" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E252" s="4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="253" spans="1:4">
+    <row r="253" spans="1:5">
       <c r="A253" s="2">
         <v>38668</v>
       </c>
@@ -5317,11 +6186,14 @@
       <c r="C253" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D253" s="4" t="s">
+      <c r="D253" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E253" s="4" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="254" spans="1:4">
+    <row r="254" spans="1:5">
       <c r="A254" s="2">
         <v>38674</v>
       </c>
@@ -5331,11 +6203,14 @@
       <c r="C254" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D254" s="4" t="s">
+      <c r="D254" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E254" s="4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="255" spans="1:4">
+    <row r="255" spans="1:5">
       <c r="A255" s="2">
         <v>38676</v>
       </c>
@@ -5345,11 +6220,14 @@
       <c r="C255" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D255" s="4" t="s">
+      <c r="D255" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E255" s="4" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="256" spans="1:4">
+    <row r="256" spans="1:5">
       <c r="A256" s="2">
         <v>38677</v>
       </c>
@@ -5359,11 +6237,14 @@
       <c r="C256" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D256" s="4" t="s">
+      <c r="D256" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E256" s="4" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="257" spans="1:4">
+    <row r="257" spans="1:5">
       <c r="A257" s="2">
         <v>38678</v>
       </c>
@@ -5373,11 +6254,14 @@
       <c r="C257" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D257" s="4" t="s">
+      <c r="D257" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E257" s="4" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="258" spans="1:4">
+    <row r="258" spans="1:5">
       <c r="A258" s="2">
         <v>38681</v>
       </c>
@@ -5387,11 +6271,14 @@
       <c r="C258" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D258" s="4" t="s">
+      <c r="D258" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E258" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="259" spans="1:4">
+    <row r="259" spans="1:5">
       <c r="A259" s="2">
         <v>38684</v>
       </c>
@@ -5401,11 +6288,14 @@
       <c r="C259" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D259" s="4" t="s">
+      <c r="D259" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E259" s="4" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="260" spans="1:4">
+    <row r="260" spans="1:5">
       <c r="A260" s="2">
         <v>38691</v>
       </c>
@@ -5415,11 +6305,14 @@
       <c r="C260" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D260" s="4" t="s">
+      <c r="D260" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E260" s="4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="261" spans="1:4">
+    <row r="261" spans="1:5">
       <c r="A261" s="2">
         <v>38692</v>
       </c>
@@ -5429,11 +6322,14 @@
       <c r="C261" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D261" s="4" t="s">
+      <c r="D261" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E261" s="4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="262" spans="1:4">
+    <row r="262" spans="1:5">
       <c r="A262" s="2">
         <v>38694</v>
       </c>
@@ -5443,11 +6339,14 @@
       <c r="C262" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D262" s="4" t="s">
+      <c r="D262" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E262" s="4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="263" spans="1:4">
+    <row r="263" spans="1:5">
       <c r="A263" s="2">
         <v>38695</v>
       </c>
@@ -5457,11 +6356,14 @@
       <c r="C263" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D263" s="4" t="s">
+      <c r="D263" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E263" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="264" spans="1:4">
+    <row r="264" spans="1:5">
       <c r="A264" s="2">
         <v>38704</v>
       </c>
@@ -5471,11 +6373,14 @@
       <c r="C264" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D264" s="4" t="s">
+      <c r="D264" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E264" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="265" spans="1:4">
+    <row r="265" spans="1:5">
       <c r="A265" s="2">
         <v>38709</v>
       </c>
@@ -5485,11 +6390,14 @@
       <c r="C265" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D265" s="4" t="s">
+      <c r="D265" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E265" s="4" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="266" spans="1:4">
+    <row r="266" spans="1:5">
       <c r="A266" s="2">
         <v>38715</v>
       </c>
@@ -5499,11 +6407,14 @@
       <c r="C266" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D266" s="4" t="s">
+      <c r="D266" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E266" s="4" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="267" spans="1:4">
+    <row r="267" spans="1:5">
       <c r="A267" s="2">
         <v>38716</v>
       </c>
@@ -5513,11 +6424,14 @@
       <c r="C267" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D267" s="4" t="s">
+      <c r="D267" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E267" s="4" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="268" spans="1:4">
+    <row r="268" spans="1:5">
       <c r="A268" s="2">
         <v>38717</v>
       </c>
@@ -5527,11 +6441,14 @@
       <c r="C268" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D268" s="4" t="s">
+      <c r="D268" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E268" s="4" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="269" spans="1:4">
+    <row r="269" spans="1:5">
       <c r="A269" s="2">
         <v>38718</v>
       </c>
@@ -5541,11 +6458,14 @@
       <c r="C269" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D269" s="4" t="s">
+      <c r="D269" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E269" s="4" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="270" spans="1:4">
+    <row r="270" spans="1:5">
       <c r="A270" s="2">
         <v>38719</v>
       </c>
@@ -5555,11 +6475,14 @@
       <c r="C270" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D270" s="4" t="s">
+      <c r="D270" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E270" s="4" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="271" spans="1:4">
+    <row r="271" spans="1:5">
       <c r="A271" s="2">
         <v>38720</v>
       </c>
@@ -5569,11 +6492,14 @@
       <c r="C271" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D271" s="4" t="s">
+      <c r="D271" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E271" s="4" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="272" spans="1:4">
+    <row r="272" spans="1:5">
       <c r="A272" s="2">
         <v>38722</v>
       </c>
@@ -5583,11 +6509,14 @@
       <c r="C272" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D272" s="4" t="s">
+      <c r="D272" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E272" s="4" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="273" spans="1:4">
+    <row r="273" spans="1:5">
       <c r="A273" s="2">
         <v>38725</v>
       </c>
@@ -5597,11 +6526,14 @@
       <c r="C273" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D273" s="4" t="s">
+      <c r="D273" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E273" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="274" spans="1:4">
+    <row r="274" spans="1:5">
       <c r="A274" s="2">
         <v>38727</v>
       </c>
@@ -5611,11 +6543,14 @@
       <c r="C274" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D274" s="4" t="s">
+      <c r="D274" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E274" s="4" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="275" spans="1:4">
+    <row r="275" spans="1:5">
       <c r="A275" s="2">
         <v>38730</v>
       </c>
@@ -5625,11 +6560,14 @@
       <c r="C275" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D275" s="4" t="s">
+      <c r="D275" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E275" s="4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="276" spans="1:4">
+    <row r="276" spans="1:5">
       <c r="A276" s="2">
         <v>38746</v>
       </c>
@@ -5639,11 +6577,14 @@
       <c r="C276" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D276" s="4" t="s">
+      <c r="D276" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E276" s="4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="277" spans="1:4">
+    <row r="277" spans="1:5">
       <c r="A277" s="2">
         <v>38747</v>
       </c>
@@ -5653,11 +6594,14 @@
       <c r="C277" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D277" s="4" t="s">
+      <c r="D277" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E277" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="278" spans="1:4">
+    <row r="278" spans="1:5">
       <c r="A278" s="2">
         <v>38749</v>
       </c>
@@ -5667,11 +6611,14 @@
       <c r="C278" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D278" s="4" t="s">
+      <c r="D278" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E278" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="279" spans="1:4">
+    <row r="279" spans="1:5">
       <c r="A279" s="2">
         <v>38751</v>
       </c>
@@ -5681,11 +6628,14 @@
       <c r="C279" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D279" s="4" t="s">
+      <c r="D279" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E279" s="4" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="280" spans="1:4">
+    <row r="280" spans="1:5">
       <c r="A280" s="2">
         <v>38752</v>
       </c>
@@ -5695,11 +6645,14 @@
       <c r="C280" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D280" s="4" t="s">
+      <c r="D280" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E280" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="281" spans="1:4">
+    <row r="281" spans="1:5">
       <c r="A281" s="2">
         <v>38755</v>
       </c>
@@ -5709,11 +6662,14 @@
       <c r="C281" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D281" s="4" t="s">
+      <c r="D281" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E281" s="4" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="282" spans="1:4">
+    <row r="282" spans="1:5">
       <c r="A282" s="2">
         <v>38762</v>
       </c>
@@ -5723,11 +6679,14 @@
       <c r="C282" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D282" s="4" t="s">
+      <c r="D282" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E282" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="283" spans="1:4">
+    <row r="283" spans="1:5">
       <c r="A283" s="2">
         <v>38764</v>
       </c>
@@ -5737,11 +6696,14 @@
       <c r="C283" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D283" s="4" t="s">
+      <c r="D283" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E283" s="4" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="284" spans="1:4">
+    <row r="284" spans="1:5">
       <c r="A284" s="2">
         <v>38769</v>
       </c>
@@ -5751,11 +6713,14 @@
       <c r="C284" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D284" s="4" t="s">
+      <c r="D284" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E284" s="4" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="285" spans="1:4">
+    <row r="285" spans="1:5">
       <c r="A285" s="2">
         <v>38770</v>
       </c>
@@ -5765,11 +6730,14 @@
       <c r="C285" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D285" s="4" t="s">
+      <c r="D285" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E285" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="286" spans="1:4">
+    <row r="286" spans="1:5">
       <c r="A286" s="2">
         <v>38771</v>
       </c>
@@ -5779,11 +6747,14 @@
       <c r="C286" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D286" s="4" t="s">
+      <c r="D286" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="E286" s="4" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="287" spans="1:4">
+    <row r="287" spans="1:5">
       <c r="A287" s="2">
         <v>38772</v>
       </c>
@@ -5793,11 +6764,14 @@
       <c r="C287" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D287" s="4" t="s">
+      <c r="D287" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="E287" s="4" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="288" spans="1:4">
+    <row r="288" spans="1:5">
       <c r="A288" s="2">
         <v>38773</v>
       </c>
@@ -5807,11 +6781,14 @@
       <c r="C288" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D288" s="4" t="s">
+      <c r="D288" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E288" s="4" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="289" spans="1:4">
+    <row r="289" spans="1:5">
       <c r="A289" s="2">
         <v>38777</v>
       </c>
@@ -5821,11 +6798,14 @@
       <c r="C289" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D289" s="4" t="s">
+      <c r="D289" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E289" s="4" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="290" spans="1:4">
+    <row r="290" spans="1:5">
       <c r="A290" s="2">
         <v>38780</v>
       </c>
@@ -5835,11 +6815,14 @@
       <c r="C290" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D290" s="4" t="s">
+      <c r="D290" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E290" s="4" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="291" spans="1:4">
+    <row r="291" spans="1:5">
       <c r="A291" s="2">
         <v>38784</v>
       </c>
@@ -5849,11 +6832,14 @@
       <c r="C291" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D291" s="4" t="s">
+      <c r="D291" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E291" s="4" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="292" spans="1:4">
+    <row r="292" spans="1:5">
       <c r="A292" s="2">
         <v>38785</v>
       </c>
@@ -5863,11 +6849,14 @@
       <c r="C292" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D292" s="4" t="s">
+      <c r="D292" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E292" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="293" spans="1:4">
+    <row r="293" spans="1:5">
       <c r="A293" s="2">
         <v>38791</v>
       </c>
@@ -5877,11 +6866,14 @@
       <c r="C293" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D293" s="4" t="s">
+      <c r="D293" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E293" s="4" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="294" spans="1:4">
+    <row r="294" spans="1:5">
       <c r="A294" s="2">
         <v>38792</v>
       </c>
@@ -5891,11 +6883,14 @@
       <c r="C294" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D294" s="4" t="s">
+      <c r="D294" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E294" s="4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="295" spans="1:4">
+    <row r="295" spans="1:5">
       <c r="A295" s="2">
         <v>38795</v>
       </c>
@@ -5905,11 +6900,14 @@
       <c r="C295" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D295" s="4" t="s">
+      <c r="D295" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E295" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="296" spans="1:4">
+    <row r="296" spans="1:5">
       <c r="A296" s="2">
         <v>38796</v>
       </c>
@@ -5919,11 +6917,14 @@
       <c r="C296" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D296" s="4" t="s">
+      <c r="D296" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E296" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="297" spans="1:4">
+    <row r="297" spans="1:5">
       <c r="A297" s="2">
         <v>38798</v>
       </c>
@@ -5933,11 +6934,14 @@
       <c r="C297" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D297" s="4" t="s">
+      <c r="D297" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E297" s="4" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="298" spans="1:4">
+    <row r="298" spans="1:5">
       <c r="A298" s="2">
         <v>38799</v>
       </c>
@@ -5947,11 +6951,14 @@
       <c r="C298" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D298" s="4" t="s">
+      <c r="D298" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E298" s="4" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="299" spans="1:4">
+    <row r="299" spans="1:5">
       <c r="A299" s="2">
         <v>38800</v>
       </c>
@@ -5961,11 +6968,14 @@
       <c r="C299" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D299" s="4" t="s">
+      <c r="D299" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E299" s="4" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="300" spans="1:4">
+    <row r="300" spans="1:5">
       <c r="A300" s="2">
         <v>38801</v>
       </c>
@@ -5975,11 +6985,14 @@
       <c r="C300" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D300" s="4" t="s">
+      <c r="D300" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E300" s="4" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="301" spans="1:4">
+    <row r="301" spans="1:5">
       <c r="A301" s="2">
         <v>38803</v>
       </c>
@@ -5989,11 +7002,14 @@
       <c r="C301" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D301" s="4" t="s">
+      <c r="D301" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E301" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="302" spans="1:4">
+    <row r="302" spans="1:5">
       <c r="A302" s="2">
         <v>38806</v>
       </c>
@@ -6003,11 +7019,14 @@
       <c r="C302" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D302" s="4" t="s">
+      <c r="D302" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E302" s="4" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="303" spans="1:4">
+    <row r="303" spans="1:5">
       <c r="A303" s="2">
         <v>38810</v>
       </c>
@@ -6017,11 +7036,14 @@
       <c r="C303" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D303" s="4" t="s">
+      <c r="D303" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E303" s="4" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="304" spans="1:4">
+    <row r="304" spans="1:5">
       <c r="A304" s="2">
         <v>38811</v>
       </c>
@@ -6031,11 +7053,14 @@
       <c r="C304" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D304" s="4" t="s">
+      <c r="D304" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E304" s="4" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="305" spans="1:4">
+    <row r="305" spans="1:5">
       <c r="A305" s="2">
         <v>38815</v>
       </c>
@@ -6045,11 +7070,14 @@
       <c r="C305" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D305" s="4" t="s">
+      <c r="D305" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E305" s="4" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="306" spans="1:4">
+    <row r="306" spans="1:5">
       <c r="A306" s="2">
         <v>38817</v>
       </c>
@@ -6059,11 +7087,14 @@
       <c r="C306" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D306" s="4" t="s">
+      <c r="D306" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E306" s="4" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="307" spans="1:4">
+    <row r="307" spans="1:5">
       <c r="A307" s="2">
         <v>38829</v>
       </c>
@@ -6073,11 +7104,14 @@
       <c r="C307" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D307" s="4" t="s">
+      <c r="D307" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E307" s="4" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="308" spans="1:4">
+    <row r="308" spans="1:5">
       <c r="A308" s="2">
         <v>38837</v>
       </c>
@@ -6087,11 +7121,14 @@
       <c r="C308" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D308" s="4" t="s">
+      <c r="D308" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E308" s="4" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="309" spans="1:4">
+    <row r="309" spans="1:5">
       <c r="A309" s="2">
         <v>38841</v>
       </c>
@@ -6101,11 +7138,14 @@
       <c r="C309" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D309" s="4" t="s">
+      <c r="D309" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E309" s="4" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="310" spans="1:4">
+    <row r="310" spans="1:5">
       <c r="A310" s="2">
         <v>38845</v>
       </c>
@@ -6115,11 +7155,14 @@
       <c r="C310" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D310" s="4" t="s">
+      <c r="D310" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E310" s="4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="311" spans="1:4">
+    <row r="311" spans="1:5">
       <c r="A311" s="2">
         <v>38847</v>
       </c>
@@ -6129,11 +7172,14 @@
       <c r="C311" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D311" s="4" t="s">
+      <c r="D311" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E311" s="4" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="312" spans="1:4">
+    <row r="312" spans="1:5">
       <c r="A312" s="2">
         <v>38850</v>
       </c>
@@ -6143,11 +7189,14 @@
       <c r="C312" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D312" s="4" t="s">
+      <c r="D312" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E312" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="313" spans="1:4">
+    <row r="313" spans="1:5">
       <c r="A313" s="2">
         <v>38855</v>
       </c>
@@ -6157,11 +7206,14 @@
       <c r="C313" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D313" s="4" t="s">
+      <c r="D313" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E313" s="4" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="314" spans="1:4">
+    <row r="314" spans="1:5">
       <c r="A314" s="2">
         <v>38856</v>
       </c>
@@ -6171,11 +7223,14 @@
       <c r="C314" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D314" s="4" t="s">
+      <c r="D314" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="E314" s="4" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="315" spans="1:4">
+    <row r="315" spans="1:5">
       <c r="A315" s="2">
         <v>38858</v>
       </c>
@@ -6185,11 +7240,14 @@
       <c r="C315" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D315" s="4" t="s">
+      <c r="D315" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E315" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="316" spans="1:4">
+    <row r="316" spans="1:5">
       <c r="A316" s="2">
         <v>38859</v>
       </c>
@@ -6199,11 +7257,14 @@
       <c r="C316" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D316" s="4" t="s">
+      <c r="D316" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E316" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="317" spans="1:4">
+    <row r="317" spans="1:5">
       <c r="A317" s="2">
         <v>38862</v>
       </c>
@@ -6213,11 +7274,14 @@
       <c r="C317" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D317" s="4" t="s">
+      <c r="D317" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E317" s="4" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="318" spans="1:4">
+    <row r="318" spans="1:5">
       <c r="A318" s="2">
         <v>38866</v>
       </c>
@@ -6227,11 +7291,14 @@
       <c r="C318" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D318" s="4" t="s">
+      <c r="D318" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E318" s="4" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="319" spans="1:4">
+    <row r="319" spans="1:5">
       <c r="A319" s="2">
         <v>38888</v>
       </c>
@@ -6241,11 +7308,14 @@
       <c r="C319" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D319" s="4" t="s">
+      <c r="D319" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E319" s="4" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="320" spans="1:4">
+    <row r="320" spans="1:5">
       <c r="A320" s="2">
         <v>38894</v>
       </c>
@@ -6255,11 +7325,14 @@
       <c r="C320" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D320" s="4" t="s">
+      <c r="D320" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E320" s="4" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="321" spans="1:4">
+    <row r="321" spans="1:5">
       <c r="A321" s="2">
         <v>38896</v>
       </c>
@@ -6269,11 +7342,14 @@
       <c r="C321" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D321" s="4" t="s">
+      <c r="D321" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E321" s="4" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="322" spans="1:4">
+    <row r="322" spans="1:5">
       <c r="A322" s="2">
         <v>38903</v>
       </c>
@@ -6283,11 +7359,14 @@
       <c r="C322" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D322" s="4" t="s">
+      <c r="D322" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E322" s="4" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="323" spans="1:4">
+    <row r="323" spans="1:5">
       <c r="A323" s="2">
         <v>38906</v>
       </c>
@@ -6297,11 +7376,14 @@
       <c r="C323" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D323" s="4" t="s">
+      <c r="D323" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E323" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="324" spans="1:4">
+    <row r="324" spans="1:5">
       <c r="A324" s="2">
         <v>38914</v>
       </c>
@@ -6311,11 +7393,14 @@
       <c r="C324" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D324" s="4" t="s">
+      <c r="D324" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="E324" s="4" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="325" spans="1:4">
+    <row r="325" spans="1:5">
       <c r="A325" s="2">
         <v>38915</v>
       </c>
@@ -6325,11 +7410,14 @@
       <c r="C325" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D325" s="4" t="s">
+      <c r="D325" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="E325" s="4" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="326" spans="1:4">
+    <row r="326" spans="1:5">
       <c r="A326" s="2">
         <v>38918</v>
       </c>
@@ -6339,11 +7427,14 @@
       <c r="C326" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D326" s="4" t="s">
+      <c r="D326" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E326" s="4" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="327" spans="1:4">
+    <row r="327" spans="1:5">
       <c r="A327" s="2">
         <v>38924</v>
       </c>
@@ -6353,11 +7444,14 @@
       <c r="C327" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D327" s="4" t="s">
+      <c r="D327" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E327" s="4" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="328" spans="1:4">
+    <row r="328" spans="1:5">
       <c r="A328" s="2">
         <v>38925</v>
       </c>
@@ -6367,11 +7461,14 @@
       <c r="C328" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D328" s="4" t="s">
+      <c r="D328" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E328" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="329" spans="1:4">
+    <row r="329" spans="1:5">
       <c r="A329" s="2">
         <v>38929</v>
       </c>
@@ -6381,11 +7478,14 @@
       <c r="C329" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D329" s="4" t="s">
+      <c r="D329" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E329" s="4" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="330" spans="1:4">
+    <row r="330" spans="1:5">
       <c r="A330" s="2">
         <v>38930</v>
       </c>
@@ -6395,11 +7495,14 @@
       <c r="C330" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D330" s="4" t="s">
+      <c r="D330" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E330" s="4" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="331" spans="1:4">
+    <row r="331" spans="1:5">
       <c r="A331" s="2">
         <v>38937</v>
       </c>
@@ -6409,11 +7512,14 @@
       <c r="C331" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D331" s="4" t="s">
+      <c r="D331" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E331" s="4" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="332" spans="1:4">
+    <row r="332" spans="1:5">
       <c r="A332" s="2">
         <v>38941</v>
       </c>
@@ -6423,11 +7529,14 @@
       <c r="C332" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D332" s="4" t="s">
+      <c r="D332" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E332" s="4" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="333" spans="1:4">
+    <row r="333" spans="1:5">
       <c r="A333" s="2">
         <v>38943</v>
       </c>
@@ -6437,11 +7546,14 @@
       <c r="C333" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D333" s="4" t="s">
+      <c r="D333" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E333" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="334" spans="1:4">
+    <row r="334" spans="1:5">
       <c r="A334" s="2">
         <v>38951</v>
       </c>
@@ -6451,11 +7563,14 @@
       <c r="C334" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D334" s="4" t="s">
+      <c r="D334" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E334" s="4" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="335" spans="1:4">
+    <row r="335" spans="1:5">
       <c r="A335" s="2">
         <v>38954</v>
       </c>
@@ -6465,11 +7580,14 @@
       <c r="C335" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D335" s="4" t="s">
+      <c r="D335" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E335" s="4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="336" spans="1:4">
+    <row r="336" spans="1:5">
       <c r="A336" s="2">
         <v>38957</v>
       </c>
@@ -6479,11 +7597,14 @@
       <c r="C336" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D336" s="4" t="s">
+      <c r="D336" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E336" s="4" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="337" spans="1:4">
+    <row r="337" spans="1:5">
       <c r="A337" s="2">
         <v>38964</v>
       </c>
@@ -6493,11 +7614,14 @@
       <c r="C337" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D337" s="4" t="s">
+      <c r="D337" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E337" s="4" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="338" spans="1:4">
+    <row r="338" spans="1:5">
       <c r="A338" s="2">
         <v>38965</v>
       </c>
@@ -6507,11 +7631,14 @@
       <c r="C338" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D338" s="4" t="s">
+      <c r="D338" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E338" s="4" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="339" spans="1:4">
+    <row r="339" spans="1:5">
       <c r="A339" s="2">
         <v>38982</v>
       </c>
@@ -6521,11 +7648,14 @@
       <c r="C339" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D339" s="4" t="s">
+      <c r="D339" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E339" s="4" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="340" spans="1:4">
+    <row r="340" spans="1:5">
       <c r="A340" s="2">
         <v>38987</v>
       </c>
@@ -6535,11 +7665,14 @@
       <c r="C340" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D340" s="4" t="s">
+      <c r="D340" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E340" s="4" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="341" spans="1:4">
+    <row r="341" spans="1:5">
       <c r="A341" s="2">
         <v>38992</v>
       </c>
@@ -6549,11 +7682,14 @@
       <c r="C341" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D341" s="4" t="s">
+      <c r="D341" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E341" s="4" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="342" spans="1:4">
+    <row r="342" spans="1:5">
       <c r="A342" s="2">
         <v>38995</v>
       </c>
@@ -6563,11 +7699,14 @@
       <c r="C342" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D342" s="4" t="s">
+      <c r="D342" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E342" s="4" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="343" spans="1:4">
+    <row r="343" spans="1:5">
       <c r="A343" s="2">
         <v>38996</v>
       </c>
@@ -6577,11 +7716,14 @@
       <c r="C343" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D343" s="4" t="s">
+      <c r="D343" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E343" s="4" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="344" spans="1:4">
+    <row r="344" spans="1:5">
       <c r="A344" s="2">
         <v>43011</v>
       </c>
@@ -6591,11 +7733,14 @@
       <c r="C344" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D344" s="4" t="s">
+      <c r="D344" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E344" s="4" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="345" spans="1:4">
+    <row r="345" spans="1:5">
       <c r="A345" s="2">
         <v>43025</v>
       </c>
@@ -6605,11 +7750,14 @@
       <c r="C345" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D345" s="4" t="s">
+      <c r="D345" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E345" s="4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="346" spans="1:4">
+    <row r="346" spans="1:5">
       <c r="A346" s="2">
         <v>43026</v>
       </c>
@@ -6619,11 +7767,14 @@
       <c r="C346" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D346" s="4" t="s">
+      <c r="D346" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E346" s="4" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="347" spans="1:4">
+    <row r="347" spans="1:5">
       <c r="A347" s="2">
         <v>43034</v>
       </c>
@@ -6633,11 +7784,14 @@
       <c r="C347" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D347" s="4" t="s">
+      <c r="D347" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E347" s="4" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="348" spans="1:4">
+    <row r="348" spans="1:5">
       <c r="A348" s="2">
         <v>43041</v>
       </c>
@@ -6647,11 +7801,14 @@
       <c r="C348" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D348" s="4" t="s">
+      <c r="D348" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E348" s="4" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="349" spans="1:4">
+    <row r="349" spans="1:5">
       <c r="A349" s="2">
         <v>43043</v>
       </c>
@@ -6661,11 +7818,14 @@
       <c r="C349" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D349" s="4" t="s">
+      <c r="D349" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E349" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="350" spans="1:4">
+    <row r="350" spans="1:5">
       <c r="A350" s="2">
         <v>43045</v>
       </c>
@@ -6675,11 +7835,14 @@
       <c r="C350" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D350" s="4" t="s">
+      <c r="D350" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E350" s="4" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="351" spans="1:4">
+    <row r="351" spans="1:5">
       <c r="A351" s="2">
         <v>43058</v>
       </c>
@@ -6689,11 +7852,14 @@
       <c r="C351" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D351" s="4" t="s">
+      <c r="D351" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E351" s="4" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="352" spans="1:4">
+    <row r="352" spans="1:5">
       <c r="A352" s="2">
         <v>43059</v>
       </c>
@@ -6703,11 +7869,14 @@
       <c r="C352" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D352" s="4" t="s">
+      <c r="D352" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E352" s="4" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="353" spans="1:4">
+    <row r="353" spans="1:5">
       <c r="A353" s="2">
         <v>43068</v>
       </c>
@@ -6717,11 +7886,14 @@
       <c r="C353" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D353" s="4" t="s">
+      <c r="D353" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E353" s="4" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="354" spans="1:4">
+    <row r="354" spans="1:5">
       <c r="A354" s="2">
         <v>43070</v>
       </c>
@@ -6731,11 +7903,14 @@
       <c r="C354" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D354" s="4" t="s">
+      <c r="D354" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E354" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="355" spans="1:4">
+    <row r="355" spans="1:5">
       <c r="A355" s="2">
         <v>43105</v>
       </c>
@@ -6745,11 +7920,14 @@
       <c r="C355" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D355" s="4" t="s">
+      <c r="D355" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E355" s="4" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="356" spans="1:4">
+    <row r="356" spans="1:5">
       <c r="A356" s="2">
         <v>43107</v>
       </c>
@@ -6759,11 +7937,14 @@
       <c r="C356" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D356" s="4" t="s">
+      <c r="D356" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E356" s="4" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="357" spans="1:4">
+    <row r="357" spans="1:5">
       <c r="A357" s="2">
         <v>43111</v>
       </c>
@@ -6773,11 +7954,14 @@
       <c r="C357" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D357" s="4" t="s">
+      <c r="D357" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E357" s="4" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="358" spans="1:4">
+    <row r="358" spans="1:5">
       <c r="A358" s="2">
         <v>43123</v>
       </c>
@@ -6787,11 +7971,14 @@
       <c r="C358" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D358" s="4" t="s">
+      <c r="D358" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E358" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="359" spans="1:4">
+    <row r="359" spans="1:5">
       <c r="A359" s="2">
         <v>43130</v>
       </c>
@@ -6801,11 +7988,14 @@
       <c r="C359" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D359" s="4" t="s">
+      <c r="D359" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E359" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="360" spans="1:4">
+    <row r="360" spans="1:5">
       <c r="A360" s="2">
         <v>43132</v>
       </c>
@@ -6815,11 +8005,14 @@
       <c r="C360" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D360" s="4" t="s">
+      <c r="D360" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E360" s="4" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="361" spans="1:4">
+    <row r="361" spans="1:5">
       <c r="A361" s="2">
         <v>43142</v>
       </c>
@@ -6829,11 +8022,14 @@
       <c r="C361" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D361" s="4" t="s">
+      <c r="D361" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E361" s="4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="362" spans="1:4">
+    <row r="362" spans="1:5">
       <c r="A362" s="2">
         <v>43147</v>
       </c>
@@ -6843,11 +8039,14 @@
       <c r="C362" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D362" s="4" t="s">
+      <c r="D362" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E362" s="4" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="363" spans="1:4">
+    <row r="363" spans="1:5">
       <c r="A363" s="2">
         <v>43152</v>
       </c>
@@ -6857,11 +8056,14 @@
       <c r="C363" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D363" s="4" t="s">
+      <c r="D363" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E363" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="364" spans="1:4">
+    <row r="364" spans="1:5">
       <c r="A364" s="2">
         <v>43159</v>
       </c>
@@ -6871,11 +8073,14 @@
       <c r="C364" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D364" s="4" t="s">
+      <c r="D364" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E364" s="4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="365" spans="1:4">
+    <row r="365" spans="1:5">
       <c r="A365" s="2">
         <v>43162</v>
       </c>
@@ -6885,11 +8090,14 @@
       <c r="C365" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D365" s="4" t="s">
+      <c r="D365" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E365" s="4" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="366" spans="1:4">
+    <row r="366" spans="1:5">
       <c r="A366" s="2">
         <v>43163</v>
       </c>
@@ -6899,11 +8107,14 @@
       <c r="C366" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D366" s="4" t="s">
+      <c r="D366" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E366" s="4" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="367" spans="1:4">
+    <row r="367" spans="1:5">
       <c r="A367" s="2">
         <v>43164</v>
       </c>
@@ -6913,11 +8124,14 @@
       <c r="C367" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D367" s="4" t="s">
+      <c r="D367" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E367" s="4" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="368" spans="1:4">
+    <row r="368" spans="1:5">
       <c r="A368" s="2">
         <v>43169</v>
       </c>
@@ -6927,11 +8141,14 @@
       <c r="C368" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D368" s="4" t="s">
+      <c r="D368" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E368" s="4" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="369" spans="1:4">
+    <row r="369" spans="1:5">
       <c r="A369" s="2">
         <v>43183</v>
       </c>
@@ -6941,11 +8158,14 @@
       <c r="C369" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D369" s="4" t="s">
+      <c r="D369" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E369" s="4" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="370" spans="1:4">
+    <row r="370" spans="1:5">
       <c r="A370" s="2">
         <v>43188</v>
       </c>
@@ -6955,11 +8175,14 @@
       <c r="C370" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D370" s="4" t="s">
+      <c r="D370" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E370" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="371" spans="1:4">
+    <row r="371" spans="1:5">
       <c r="A371" s="2">
         <v>43193</v>
       </c>
@@ -6969,11 +8192,14 @@
       <c r="C371" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D371" s="4" t="s">
+      <c r="D371" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E371" s="4" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="372" spans="1:4">
+    <row r="372" spans="1:5">
       <c r="A372" s="2">
         <v>43194</v>
       </c>
@@ -6983,11 +8209,14 @@
       <c r="C372" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D372" s="4" t="s">
+      <c r="D372" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E372" s="4" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="373" spans="1:4">
+    <row r="373" spans="1:5">
       <c r="A373" s="2">
         <v>43195</v>
       </c>
@@ -6997,7 +8226,10 @@
       <c r="C373" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D373" s="4" t="s">
+      <c r="D373" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E373" s="4" t="s">
         <v>92</v>
       </c>
     </row>
@@ -7025,5 +8257,6 @@
     <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>